--- a/demo_action_result.xlsx
+++ b/demo_action_result.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>远坂凛</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D9" t="n">
